--- a/imports/registry-lab/data/agriculture/farmer-registry.xlsx
+++ b/imports/registry-lab/data/agriculture/farmer-registry.xlsx
@@ -2141,22 +2141,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="35" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2172,55 +2173,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>subject_scope</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>subject_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>purpose_code</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>lawful_basis_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>legal_instrument_reference</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>grantee_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disclosure_mode</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>valid_from</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>valid_until</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captured_by</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>withdrawal_allowed</t>
         </is>
@@ -2239,51 +2245,56 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>climate-smart-input-support</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>program_rule</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>AG-PROG-2026A-RULES</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>government_program</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="L2" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>North District Agriculture Office</t>
         </is>
       </c>
-      <c r="M2" t="b">
+      <c r="N2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2300,51 +2311,56 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>program</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>climate-smart-input-support</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>public_task</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>NAGDI-PUBLIC-SERVICE-2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>government_program</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="K3" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="L3" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>East District Agriculture Office</t>
         </is>
       </c>
-      <c r="M3" t="b">
+      <c r="N3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2361,51 +2377,56 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>climate-smart-input-support</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>program_rule</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>AG-PROG-2026A-RULES</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>government_program</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>North District Agriculture Office</t>
         </is>
       </c>
-      <c r="M4" t="b">
+      <c r="N4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2422,51 +2443,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>climate-smart-input-support</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>program_rule</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>AG-PROG-2026A-RULES</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>government_program</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>45658</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>46022</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>South District Agriculture Office</t>
         </is>
       </c>
-      <c r="M5" t="b">
+      <c r="N5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2483,51 +2509,56 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>climate-smart-input-support</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>consent</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>CONSENT-CAPTURE-2026-03</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>government_program</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <v>46295</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>West District Agriculture Office</t>
         </is>
       </c>
-      <c r="M6" t="b">
+      <c r="N6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2544,51 +2575,56 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>program</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>livestock-movement-permit-review</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>permit_condition</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>ANIMAL-HEALTH-PERMIT-REG-2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>animal_health_authority</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>redacted_result</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Central Animal Health Office</t>
         </is>
       </c>
-      <c r="M7" t="b">
+      <c r="N7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2605,51 +2641,56 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>universal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>livestock-movement-permit-review</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>legal_mandate</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ANIMAL-HEALTH-ACT-14</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>animal_health_authority</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>redacted_result</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Central Animal Health Office</t>
         </is>
       </c>
-      <c r="M8" t="b">
+      <c r="N8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2666,51 +2707,56 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>universal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>farmer</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>livestock-movement-permit-review</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>vital_public_interest</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ANIMAL-HEALTH-OUTBREAK-ORDER-2026-04</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>animal_health_authority</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>redacted_result</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>North Animal Health Office</t>
         </is>
       </c>
-      <c r="M9" t="b">
+      <c r="N9" t="b">
         <v>0</v>
       </c>
     </row>
